--- a/PPG/Financiadores.xlsx
+++ b/PPG/Financiadores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97A6BBD-E37F-514A-95B9-F9FC875F3AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F77F3BC-0A99-294E-A3BD-7F4241AC4345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="680" windowWidth="27880" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="980" yWindow="680" windowWidth="27880" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="financiadores" sheetId="1" r:id="rId1"/>
@@ -1223,7 +1223,7 @@
     <t>Edital nº 23/2025</t>
   </si>
   <si>
-    <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2025/chamada-no-23-2025/ResultadoPreliminarChamada232025.pdf</t>
+    <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2025/chamada-no-23-2025/Resultado_Final_Chamada_23_2025.pdf</t>
   </si>
 </sst>
 </file>
@@ -8331,7 +8331,7 @@
         <v>121</v>
       </c>
       <c r="B197" s="6">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C197" s="7" t="s">
         <v>2</v>
@@ -8371,7 +8371,7 @@
         <v>121</v>
       </c>
       <c r="B198" s="6">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C198" s="7" t="s">
         <v>2</v>
@@ -8390,7 +8390,7 @@
         <v>121</v>
       </c>
       <c r="B199" s="6">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C199" s="7" t="s">
         <v>2</v>
@@ -8409,7 +8409,7 @@
         <v>121</v>
       </c>
       <c r="B200" s="6">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="C200" s="7" t="s">
         <v>2</v>
